--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2020_aysen.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2020_aysen.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>31.67267865701385</v>
+      </c>
+      <c r="C2">
         <v>23.95631006735111</v>
-      </c>
-      <c r="C2">
-        <v>31.67267865701385</v>
       </c>
       <c r="D2">
         <v>4.174265557544488</v>
       </c>
       <c r="E2">
-        <v>15.39321836099585</v>
+        <v>20.35140041493776</v>
       </c>
       <c r="F2">
         <v>64.2553812240664</v>
       </c>
       <c r="G2">
-        <v>20.35140041493776</v>
+        <v>15.39321836099585</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>28.54122621564482</v>
+      </c>
+      <c r="C3">
         <v>37.42071881606766</v>
-      </c>
-      <c r="C3">
-        <v>28.54122621564482</v>
       </c>
       <c r="D3">
         <v>2.672316384180791</v>
       </c>
       <c r="E3">
-        <v>22.54777070063695</v>
+        <v>17.19745222929937</v>
       </c>
       <c r="F3">
         <v>60.2547770700637</v>
       </c>
       <c r="G3">
-        <v>17.19745222929937</v>
+        <v>22.54777070063695</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>31.54483886034563</v>
+      </c>
+      <c r="C4">
         <v>23.26015880429706</v>
-      </c>
-      <c r="C4">
-        <v>31.54483886034563</v>
       </c>
       <c r="D4">
         <v>4.299196787148595</v>
       </c>
       <c r="E4">
-        <v>15.02545728832736</v>
+        <v>20.37714501225721</v>
       </c>
       <c r="F4">
         <v>64.59739769941542</v>
       </c>
       <c r="G4">
-        <v>20.37714501225721</v>
+        <v>15.02545728832736</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>32.72933182332956</v>
+      </c>
+      <c r="C5">
         <v>21.97055492638732</v>
-      </c>
-      <c r="C5">
-        <v>32.72933182332956</v>
       </c>
       <c r="D5">
         <v>4.551546391752577</v>
       </c>
       <c r="E5">
-        <v>14.20204978038067</v>
+        <v>21.15666178623719</v>
       </c>
       <c r="F5">
         <v>64.64128843338213</v>
       </c>
       <c r="G5">
-        <v>21.15666178623719</v>
+        <v>14.20204978038067</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>31.14909781576448</v>
+      </c>
+      <c r="C6">
         <v>17.75878442545109</v>
-      </c>
-      <c r="C6">
-        <v>31.14909781576448</v>
       </c>
       <c r="D6">
         <v>5.631016042780749</v>
       </c>
       <c r="E6">
-        <v>11.92602040816326</v>
+        <v>20.91836734693877</v>
       </c>
       <c r="F6">
         <v>67.15561224489795</v>
       </c>
       <c r="G6">
-        <v>20.91836734693877</v>
+        <v>11.92602040816326</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>33.10696095076401</v>
+      </c>
+      <c r="C7">
         <v>26.61290322580645</v>
-      </c>
-      <c r="C7">
-        <v>33.10696095076401</v>
       </c>
       <c r="D7">
         <v>3.757575757575758</v>
       </c>
       <c r="E7">
-        <v>16.6622375764018</v>
+        <v>20.72814243954291</v>
       </c>
       <c r="F7">
         <v>62.60961998405527</v>
       </c>
       <c r="G7">
-        <v>20.72814243954291</v>
+        <v>16.6622375764018</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>36.72456575682382</v>
+      </c>
+      <c r="C8">
         <v>19.35483870967742</v>
-      </c>
-      <c r="C8">
-        <v>36.72456575682382</v>
       </c>
       <c r="D8">
         <v>5.166666666666667</v>
       </c>
       <c r="E8">
-        <v>12.4006359300477</v>
+        <v>23.52941176470588</v>
       </c>
       <c r="F8">
         <v>64.06995230524642</v>
       </c>
       <c r="G8">
-        <v>23.52941176470588</v>
+        <v>12.4006359300477</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>38.88888888888889</v>
+      </c>
+      <c r="C9">
         <v>15.68627450980392</v>
-      </c>
-      <c r="C9">
-        <v>38.88888888888889</v>
       </c>
       <c r="D9">
         <v>6.375</v>
       </c>
       <c r="E9">
-        <v>10.14799154334038</v>
+        <v>25.1585623678647</v>
       </c>
       <c r="F9">
         <v>64.69344608879493</v>
       </c>
       <c r="G9">
-        <v>25.1585623678647</v>
+        <v>10.14799154334038</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>29.37019969278034</v>
+      </c>
+      <c r="C10">
         <v>36.37480798771121</v>
-      </c>
-      <c r="C10">
-        <v>29.37019969278034</v>
       </c>
       <c r="D10">
         <v>2.749155405405405</v>
       </c>
       <c r="E10">
-        <v>21.94624652455978</v>
+        <v>17.72011121408711</v>
       </c>
       <c r="F10">
         <v>60.3336422613531</v>
       </c>
       <c r="G10">
-        <v>17.72011121408711</v>
+        <v>21.94624652455978</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>28.8659793814433</v>
+      </c>
+      <c r="C11">
         <v>40.27061855670103</v>
-      </c>
-      <c r="C11">
-        <v>28.8659793814433</v>
       </c>
       <c r="D11">
         <v>2.4832</v>
       </c>
       <c r="E11">
-        <v>23.80952380952381</v>
+        <v>17.06666666666666</v>
       </c>
       <c r="F11">
         <v>59.12380952380952</v>
       </c>
       <c r="G11">
-        <v>17.06666666666666</v>
+        <v>23.80952380952381</v>
       </c>
     </row>
   </sheetData>
